--- a/output/diameter/diameter_executive_report.xlsx
+++ b/output/diameter/diameter_executive_report.xlsx
@@ -153,7 +153,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1676400"/>
+    <ext cx="3390900" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -178,7 +178,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1724025"/>
+    <ext cx="3876675" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -203,7 +203,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="4095750" cy="1981200"/>
+    <ext cx="2667000" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -228,7 +228,7 @@
       <row>22</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="3981450" cy="2095500"/>
+    <ext cx="4095750" cy="1676400"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -253,7 +253,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2266950" cy="2095500"/>
+    <ext cx="4095750" cy="1724025"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -278,7 +278,7 @@
       <row>42</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2266950" cy="2095500"/>
+    <ext cx="4095750" cy="1981200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -303,7 +303,7 @@
       <row>62</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2266950" cy="2095500"/>
+    <ext cx="3981450" cy="2095500"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
